--- a/artfynd/A 48762-2021 artfynd.xlsx
+++ b/artfynd/A 48762-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 48762-2021 artfynd.xlsx
+++ b/artfynd/A 48762-2021 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96512720</v>
+        <v>96512724</v>
       </c>
       <c r="B2" t="n">
-        <v>90138</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92205</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>366</v>
+        <v>73</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Veckticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -718,10 +713,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>379693.0185429436</v>
+        <v>379693</v>
       </c>
       <c r="R2" t="n">
-        <v>6575970.593998235</v>
+        <v>6575971</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -751,24 +746,9 @@
           <t>2021-10-07</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-10-07</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På fem asplågor</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>96512724</v>
+        <v>96512736</v>
       </c>
       <c r="B3" t="n">
-        <v>89652</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92205</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -821,12 +796,12 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Flavidoporia pulvinascens</t>
+          <t>Fomitopsis pulvinascens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pilát) Audet</t>
+          <t>(Pilát) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -835,14 +810,14 @@
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Söder Gårdsjön, Vrm</t>
+          <t>Udde i Gårdsjön, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>379693.0185429436</v>
+        <v>379913</v>
       </c>
       <c r="R3" t="n">
-        <v>6575970.593998235</v>
+        <v>6576287</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -872,19 +847,14 @@
           <t>2021-10-07</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-10-07</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På en bäverfälld asp</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,15 +882,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>96512736</v>
+        <v>96512720</v>
       </c>
       <c r="B4" t="n">
-        <v>89652</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92699</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -928,21 +893,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>73</v>
+        <v>366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Veckticka</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Flavidoporia pulvinascens</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pilát) Audet</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -951,14 +916,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Udde i Gårdsjön, Vrm</t>
+          <t>Söder Gårdsjön, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>379913.9316089909</v>
+        <v>379693</v>
       </c>
       <c r="R4" t="n">
-        <v>6576287.024736</v>
+        <v>6575971</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -988,24 +953,14 @@
           <t>2021-10-07</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-10-07</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På en bäverfälld asp</t>
+          <t>På fem asplågor</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 48762-2021 artfynd.xlsx
+++ b/artfynd/A 48762-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96512724</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96512736</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -985,8 +1000,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96512720</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>